--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/XRF/Panel 02/front/xrf_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/XRF/Panel 02/front/xrf_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.16936</v>
+        <v>16.91358</v>
       </c>
       <c r="D2" t="n">
-        <v>16.33834</v>
+        <v>16.61573</v>
       </c>
       <c r="E2" t="n">
-        <v>16.82117</v>
+        <v>16.86127</v>
       </c>
       <c r="F2" t="n">
-        <v>42.51642</v>
+        <v>42.47793</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05154</v>
+        <v>0.05067</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81709</v>
+        <v>1.82486</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.64986</v>
+        <v>17.19929</v>
       </c>
       <c r="D3" t="n">
-        <v>16.57648</v>
+        <v>16.69413</v>
       </c>
       <c r="E3" t="n">
-        <v>16.96361</v>
+        <v>16.8514</v>
       </c>
       <c r="F3" t="n">
-        <v>42.31211</v>
+        <v>42.1543</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05123</v>
+        <v>0.05103</v>
       </c>
       <c r="H3" t="n">
-        <v>1.79914</v>
+        <v>1.88167</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.56983</v>
+        <v>17.02389</v>
       </c>
       <c r="D4" t="n">
-        <v>16.66397</v>
+        <v>16.98389</v>
       </c>
       <c r="E4" t="n">
-        <v>16.70581</v>
+        <v>17.0037</v>
       </c>
       <c r="F4" t="n">
-        <v>43.47997</v>
+        <v>43.0026</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05116</v>
+        <v>0.05047</v>
       </c>
       <c r="H4" t="n">
-        <v>1.84128</v>
+        <v>1.83067</v>
       </c>
     </row>
   </sheetData>
